--- a/registration_forms/046_sustainable_supply_chain_webinar_registration--registration_forms.xlsx
+++ b/registration_forms/046_sustainable_supply_chain_webinar_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,8 +750,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,12 +779,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'supply_chain_management',_'label':_'supply_chain_management'}</t>
+          <t>supply_chain_management</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Supply Chain Management', 'label': 'Supply Chain Management'}</t>
+          <t>Supply Chain Management</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'circular_economy',_'label':_'circular_economy'}</t>
+          <t>circular_economy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Circular Economy', 'label': 'Circular Economy'}</t>
+          <t>Circular Economy</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'sustainable_production',_'label':_'sustainable_production'}</t>
+          <t>sustainable_production</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Sustainable Production', 'label': 'Sustainable Production'}</t>
+          <t>Sustainable Production</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'supply_chain_transparency',_'label':_'supply_chain_transparency'}</t>
+          <t>supply_chain_transparency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Supply Chain Transparency', 'label': 'Supply Chain Transparency'}</t>
+          <t>Supply Chain Transparency</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'supply_chain_finance',_'label':_'supply_chain_finance'}</t>
+          <t>supply_chain_finance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Supply Chain Finance', 'label': 'Supply Chain Finance'}</t>
+          <t>Supply Chain Finance</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'supply_chain_transparency',_'label':_'supply_chain_transparency'}</t>
+          <t>supply_chain_transparency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Supply Chain Transparency', 'label': 'Supply Chain Transparency'}</t>
+          <t>Supply Chain Transparency</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'supply_chain_finance',_'label':_'supply_chain_finance'}</t>
+          <t>supply_chain_finance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Supply Chain Finance', 'label': 'Supply Chain Finance'}</t>
+          <t>Supply Chain Finance</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'sustainable_production',_'label':_'sustainable_production'}</t>
+          <t>sustainable_production</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Sustainable Production', 'label': 'Sustainable Production'}</t>
+          <t>Sustainable Production</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'accept',_'label':_'accept'}</t>
+          <t>accept</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Accept', 'label': 'Accept'}</t>
+          <t>Accept</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'decline',_'label':_'decline'}</t>
+          <t>decline</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Decline', 'label': 'Decline'}</t>
+          <t>Decline</t>
         </is>
       </c>
     </row>
